--- a/database_gps.xlsx
+++ b/database_gps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\OneDrive\Desktop\U14 PISA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15191F60-4125-4D92-AC07-BBAB7C0F4EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBE3A33-DECA-4846-833D-C4CE14A8D807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anagrafica_Esercitazioni" sheetId="1" r:id="rId1"/>
@@ -38,13 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
-  <si>
-    <t>possesso 4v4 + 3j</t>
-  </si>
-  <si>
-    <t>tattica / possesso</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>mantenimento pressione e transizione</t>
   </si>
@@ -52,30 +46,15 @@
     <t>partita a tema</t>
   </si>
   <si>
-    <t>gara / alta intensità</t>
-  </si>
-  <si>
     <t>transizione negativa e attacco rapido</t>
   </si>
   <si>
     <t>navette 10-20-30</t>
   </si>
   <si>
-    <t>atletico / SSG</t>
-  </si>
-  <si>
     <t>lavoro intermittente metabolico</t>
   </si>
   <si>
-    <t>rondo 5v2</t>
-  </si>
-  <si>
-    <t>riscaldamento tecnico rapidità decisionale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tecnica / riscaldamento </t>
-  </si>
-  <si>
     <t>total dist. (m)</t>
   </si>
   <si>
@@ -116,6 +95,45 @@
   </si>
   <si>
     <t>minuti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attivazione </t>
+  </si>
+  <si>
+    <t>cerchio tecnico</t>
+  </si>
+  <si>
+    <t>tecnico-tattica</t>
+  </si>
+  <si>
+    <t>possesso</t>
+  </si>
+  <si>
+    <t>4v4 + 3j</t>
+  </si>
+  <si>
+    <t>riscaldamento tecnico</t>
+  </si>
+  <si>
+    <t>7vs6</t>
+  </si>
+  <si>
+    <t>6vs6 con meta</t>
+  </si>
+  <si>
+    <t>sviluppi di gioco - costruzione</t>
+  </si>
+  <si>
+    <t>preparazione atletica</t>
+  </si>
+  <si>
+    <t>SSG</t>
+  </si>
+  <si>
+    <t>4vs4</t>
+  </si>
+  <si>
+    <t>smarcamento</t>
   </si>
 </sst>
 </file>
@@ -124,7 +142,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -265,8 +283,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Migliaia" xfId="1" builtinId="3"/>
@@ -548,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -559,16 +577,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -576,13 +594,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
         <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -590,13 +608,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -604,13 +622,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -618,13 +636,41 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +680,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{976CCF22-2F96-4D0C-A889-6F10FC224EB2}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
@@ -651,34 +697,34 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="K1" s="4"/>
     </row>
@@ -808,6 +854,70 @@
       </c>
       <c r="J5">
         <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>3434</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -817,7 +927,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7B03B1-A124-4B1C-84EC-38D6C134DAB0}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
@@ -833,34 +943,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -1021,6 +1131,86 @@
       <c r="J5" s="8">
         <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A5, Storico_GPS!$J$2:$J$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A5, Storico_GPS!$B$2:$B$1000), 0)</f>
         <v>2.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$C$2:$C$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>100</v>
+      </c>
+      <c r="D6" s="9">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$D$2:$D$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="9">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$E$2:$E$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="F6" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$F$2:$F$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="9">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$G$2:$G$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.9</v>
+      </c>
+      <c r="H6" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$H$2:$H$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.6</v>
+      </c>
+      <c r="I6" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$I$2:$I$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="J6" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$J$2:$J$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A6, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$C$2:$C$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>286.16666666666669</v>
+      </c>
+      <c r="D7" s="9">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$D$2:$D$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="E7" s="9">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$E$2:$E$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>1.9166666666666667</v>
+      </c>
+      <c r="F7" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$F$2:$F$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="G7" s="9">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$G$2:$G$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H7" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$H$2:$H$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I7" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$I$2:$I$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J7" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$J$2:$J$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A7, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/database_gps.xlsx
+++ b/database_gps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\OneDrive\Desktop\U14 PISA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBE3A33-DECA-4846-833D-C4CE14A8D807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6161ED4C-357C-4670-A2DB-FB69D204F9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>mantenimento pressione e transizione</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t>smarcamento</t>
+  </si>
+  <si>
+    <t>11vs11</t>
+  </si>
+  <si>
+    <t>partita</t>
   </si>
 </sst>
 </file>
@@ -566,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -671,6 +677,17 @@
       </c>
       <c r="D7" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/database_gps.xlsx
+++ b/database_gps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\OneDrive\Desktop\U14 PISA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6161ED4C-357C-4670-A2DB-FB69D204F9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6503181D-5091-43E8-8591-E34D0BCE8084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anagrafica_Esercitazioni" sheetId="1" r:id="rId1"/>
@@ -697,7 +697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{976CCF22-2F96-4D0C-A889-6F10FC224EB2}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
@@ -937,6 +937,38 @@
         <v>3</v>
       </c>
     </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>2343</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+      <c r="F8">
+        <v>87</v>
+      </c>
+      <c r="G8">
+        <v>97</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -944,7 +976,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7B03B1-A124-4B1C-84EC-38D6C134DAB0}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
@@ -1230,6 +1262,46 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$C$2:$C$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>117.15</v>
+      </c>
+      <c r="D8" s="9">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$D$2:$D$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="9">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$E$2:$E$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F8" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$F$2:$F$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="G8" s="9">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$G$2:$G$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H8" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$H$2:$H$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$I$2:$I$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>1.6</v>
+      </c>
+      <c r="J8" s="8">
+        <f>IFERROR(AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$J$2:$J$1000) / AVERAGEIF(Storico_GPS!$A$2:$A$1000, A8, Storico_GPS!$B$2:$B$1000), 0)</f>
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/database_gps.xlsx
+++ b/database_gps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\OneDrive\Desktop\U14 PISA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6503181D-5091-43E8-8591-E34D0BCE8084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88783AEA-0DF7-4465-9624-206E5F33EAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,9 +146,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -289,8 +288,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Migliaia" xfId="1" builtinId="3"/>
